--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N94_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N94_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.59946961289379</v>
+        <v>4.809913812095241</v>
       </c>
       <c r="D2" t="n">
-        <v>31.49145954238433</v>
+        <v>5.117362175637455</v>
       </c>
       <c r="E2" t="n">
-        <v>7.63122411661812</v>
+        <v>1.240073918950445</v>
       </c>
       <c r="F2" t="n">
-        <v>11.4343203512289</v>
+        <v>1.858077057074696</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.58188577967216</v>
+        <v>6.757056439196726</v>
       </c>
       <c r="D3" t="n">
-        <v>57.143414481409</v>
+        <v>9.285804853228964</v>
       </c>
       <c r="E3" t="n">
-        <v>7.63122411661812</v>
+        <v>1.240073918950445</v>
       </c>
       <c r="F3" t="n">
-        <v>11.4343203512289</v>
+        <v>1.858077057074696</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.8167119617858</v>
+        <v>4.032715693790193</v>
       </c>
       <c r="D4" t="n">
-        <v>24.91080869868891</v>
+        <v>4.048006413536949</v>
       </c>
       <c r="E4" t="n">
-        <v>7.63122411661812</v>
+        <v>1.240073918950445</v>
       </c>
       <c r="F4" t="n">
-        <v>11.4343203512289</v>
+        <v>1.858077057074696</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.01421301364225</v>
+        <v>1.952309614716866</v>
       </c>
       <c r="D5" t="n">
-        <v>15.15214780595164</v>
+        <v>2.462224018467142</v>
       </c>
       <c r="E5" t="n">
-        <v>7.63122411661812</v>
+        <v>1.240073918950445</v>
       </c>
       <c r="F5" t="n">
-        <v>11.4343203512289</v>
+        <v>1.858077057074696</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.78198676309086</v>
+        <v>4.677072849002264</v>
       </c>
       <c r="D6" t="n">
-        <v>34.7599400848112</v>
+        <v>5.64849026378182</v>
       </c>
       <c r="E6" t="n">
-        <v>7.63122411661812</v>
+        <v>1.240073918950445</v>
       </c>
       <c r="F6" t="n">
-        <v>11.4343203512289</v>
+        <v>1.858077057074696</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.08710370537638</v>
+        <v>3.101654352123661</v>
       </c>
       <c r="D7" t="n">
-        <v>18.46279834276685</v>
+        <v>3.000204730699614</v>
       </c>
       <c r="E7" t="n">
-        <v>7.63122411661812</v>
+        <v>1.240073918950445</v>
       </c>
       <c r="F7" t="n">
-        <v>11.4343203512289</v>
+        <v>1.858077057074696</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.94855344885034</v>
+        <v>5.19163993543818</v>
       </c>
       <c r="D8" t="n">
-        <v>29.90516850485179</v>
+        <v>4.859589882038415</v>
       </c>
       <c r="E8" t="n">
-        <v>7.63122411661812</v>
+        <v>1.240073918950445</v>
       </c>
       <c r="F8" t="n">
-        <v>11.4343203512289</v>
+        <v>1.858077057074696</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2447948089035</v>
+        <v>3.614779156446818</v>
       </c>
       <c r="D9" t="n">
-        <v>24.74356003244566</v>
+        <v>4.02082850527242</v>
       </c>
       <c r="E9" t="n">
-        <v>7.63122411661812</v>
+        <v>1.240073918950445</v>
       </c>
       <c r="F9" t="n">
-        <v>11.4343203512289</v>
+        <v>1.858077057074696</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.28982312739008</v>
+        <v>3.784596258200887</v>
       </c>
       <c r="D10" t="n">
-        <v>21.38115056627756</v>
+        <v>3.474436967020103</v>
       </c>
       <c r="E10" t="n">
-        <v>7.63122411661812</v>
+        <v>1.240073918950445</v>
       </c>
       <c r="F10" t="n">
-        <v>11.4343203512289</v>
+        <v>1.858077057074696</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.31211597778562</v>
+        <v>4.925718846390163</v>
       </c>
       <c r="D11" t="n">
-        <v>19.20168741215288</v>
+        <v>3.120274204474843</v>
       </c>
       <c r="E11" t="n">
-        <v>7.63122411661812</v>
+        <v>1.240073918950445</v>
       </c>
       <c r="F11" t="n">
-        <v>11.4343203512289</v>
+        <v>1.858077057074696</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
